--- a/data/3.10.2/2019_France/extensions/dom_water/detail_levels.xlsx
+++ b/data/3.10.2/2019_France/extensions/dom_water/detail_levels.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A195"/>
+  <dimension ref="A1:A104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,1358 +441,721 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Water Consumption Green - Agriculture - rice</t>
+          <t>Water Consumption Blue - Agriculture - rice</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Water Consumption Green - Agriculture - wheat</t>
+          <t>Water Consumption Blue - Agriculture - wheat</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Water Consumption Green - Agriculture - other cereals</t>
+          <t>Water Consumption Blue - Agriculture - other cereals</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Water Consumption Green - Agriculture - roots and tubers</t>
+          <t>Water Consumption Blue - Agriculture - roots and tubers</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Water Consumption Green - Agriculture - sugar crops</t>
+          <t>Water Consumption Blue - Agriculture - sugar crops</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Water Consumption Green - Agriculture - pulses</t>
+          <t>Water Consumption Blue - Agriculture - pulses</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Water Consumption Green - Agriculture - nuts</t>
+          <t>Water Consumption Blue - Agriculture - nuts</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Water Consumption Green - Agriculture - oil crops</t>
+          <t>Water Consumption Blue - Agriculture - oil crops</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Water Consumption Green - Agriculture - vegetables</t>
+          <t>Water Consumption Blue - Agriculture - vegetables</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Water Consumption Green - Agriculture - fruits</t>
+          <t>Water Consumption Blue - Agriculture - fruits</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Water Consumption Green - Agriculture - fibres</t>
+          <t>Water Consumption Blue - Agriculture - fibres</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Water Consumption Green - Agriculture - other crops</t>
+          <t>Water Consumption Blue - Agriculture - other crops</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Water Consumption Green - Agriculture - fodder crops</t>
+          <t>Water Consumption Blue - Agriculture - fodder crops</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Agriculture - rice</t>
+          <t>Water Consumption Blue - Livestock - dairy cattle</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Agriculture - wheat</t>
+          <t>Water Consumption Blue - Livestock - nondairy cattle</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Agriculture - other cereals</t>
+          <t>Water Consumption Blue - Livestock - pigs</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Agriculture - roots and tubers</t>
+          <t>Water Consumption Blue - Livestock - sheep</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Agriculture - sugar crops</t>
+          <t>Water Consumption Blue - Livestock - goats</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Agriculture - pulses</t>
+          <t>Water Consumption Blue - Livestock - buffaloes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Agriculture - nuts</t>
+          <t>Water Consumption Blue - Livestock - camels</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Agriculture - oil crops</t>
+          <t>Water Consumption Blue - Livestock - horses</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Agriculture - vegetables</t>
+          <t>Water Consumption Blue - Livestock - chicken</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Agriculture - fruits</t>
+          <t>Water Consumption Blue - Livestock - turkeys</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Agriculture - fibres</t>
+          <t>Water Consumption Blue - Livestock - ducks</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Agriculture - other crops</t>
+          <t>Water Consumption Blue - Livestock - geese</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Agriculture - fodder crops</t>
+          <t>Water Consumption Blue - Manufacturing - Products of meat cattle</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Livestock - dairy cattle</t>
+          <t>Water Consumption Blue - Manufacturing - Products of meat pigs</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Livestock - nondairy cattle</t>
+          <t>Water Consumption Blue - Manufacturing - Products of meat poultry</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Livestock - pigs</t>
+          <t>Water Consumption Blue - Manufacturing - Meat products nec</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Livestock - sheep</t>
+          <t>Water Consumption Blue - Manufacturing - products of Vegetable oils and fats</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Livestock - goats</t>
+          <t>Water Consumption Blue - Manufacturing - Dairy products</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Livestock - buffaloes</t>
+          <t>Water Consumption Blue - Manufacturing - Processed rice</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Livestock - camels</t>
+          <t>Water Consumption Blue - Manufacturing - Sugar</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Livestock - horses</t>
+          <t>Water Consumption Blue - Manufacturing - Food products nec</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Livestock - chicken</t>
+          <t>Water Consumption Blue - Manufacturing - Beverages</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Livestock - turkeys</t>
+          <t>Water Consumption Blue - Manufacturing - Fish products</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Livestock - ducks</t>
+          <t>Water Consumption Blue - Manufacturing - Tobacco products (16)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Livestock - geese</t>
+          <t>Water Consumption Blue - Manufacturing - Textiles (17)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Products of meat cattle</t>
+          <t>Water Consumption Blue - Manufacturing - Wearing apparel; furs (18)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Products of meat pigs</t>
+          <t>Water Consumption Blue - Manufacturing - Leather and leather products (19)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Products of meat poultry</t>
+          <t>Water Consumption Blue - Manufacturing - Pulp</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Meat products nec</t>
+          <t>Water Consumption Blue - Manufacturing - Secondary paper for treatment, Re-processing of secondary paper into new pulp</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - products of Vegetable oils and fats</t>
+          <t>Water Consumption Blue - Manufacturing - Paper and paper products</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Dairy products</t>
+          <t>Water Consumption Blue - Manufacturing - Printed matter and recorded media (22)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Processed rice</t>
+          <t>Water Consumption Blue - Manufacturing - Plastics, basic</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Sugar</t>
+          <t>Water Consumption Blue - Manufacturing - Secondary plastic for treatment, Re-processing of secondary plastic into new plastic</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Food products nec</t>
+          <t>Water Consumption Blue - Manufacturing - N-fertiliser</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Beverages</t>
+          <t>Water Consumption Blue - Manufacturing - P- and other fertiliser</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Fish products</t>
+          <t>Water Consumption Blue - Manufacturing - Chemicals nec</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Tobacco products (16)</t>
+          <t>Water Consumption Blue - Manufacturing - Rubber and plastic products (25)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Textiles (17)</t>
+          <t>Water Consumption Blue - Manufacturing - Glass and glass products</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Wearing apparel; furs (18)</t>
+          <t>Water Consumption Blue - Manufacturing - Secondary glass for treatment, Re-processing of secondary glass into new glass</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Leather and leather products (19)</t>
+          <t>Water Consumption Blue - Manufacturing - Ceramic goods</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Pulp</t>
+          <t>Water Consumption Blue - Manufacturing - Bricks, tiles and construction products, in baked clay</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Secondary paper for treatment, Re-processing of secondary paper into new pulp</t>
+          <t>Water Consumption Blue - Manufacturing - Cement, lime and plaster</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Paper and paper products</t>
+          <t>Water Consumption Blue - Manufacturing - Ash for treatment, Re-processing of ash into clinker</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Printed matter and recorded media (22)</t>
+          <t>Water Consumption Blue - Manufacturing - Other non-metallic mineral products</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Plastics, basic</t>
+          <t>Water Consumption Blue - Manufacturing - Basic iron and steel and of ferro-alloys and first products thereof</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Secondary plastic for treatment, Re-processing of secondary plastic into new plastic</t>
+          <t>Water Consumption Blue - Manufacturing - Secondary steel for treatment, Re-processing of secondary steel into new steel</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - N-fertiliser</t>
+          <t>Water Consumption Blue - Manufacturing - Precious metals</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - P- and other fertiliser</t>
+          <t>Water Consumption Blue - Manufacturing - Secondary preciuos metals for treatment, Re-processing of secondary preciuos metals into new preciuos metals</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Chemicals nec</t>
+          <t>Water Consumption Blue - Manufacturing - Aluminium and aluminium products</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Rubber and plastic products (25)</t>
+          <t>Water Consumption Blue - Manufacturing - Secondary aluminium for treatment, Re-processing of secondary aluminium into new aluminium</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Glass and glass products</t>
+          <t>Water Consumption Blue - Manufacturing - Lead, zinc and tin and products thereof</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Secondary glass for treatment, Re-processing of secondary glass into new glass</t>
+          <t>Water Consumption Blue - Manufacturing - Secondary lead for treatment, Re-processing of secondary lead into new lead</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Ceramic goods</t>
+          <t>Water Consumption Blue - Manufacturing - Copper products</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Bricks, tiles and construction products, in baked clay</t>
+          <t>Water Consumption Blue - Manufacturing - Secondary copper for treatment, Re-processing of secondary copper into new copper</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Cement, lime and plaster</t>
+          <t>Water Consumption Blue - Manufacturing - Other non-ferrous metal products</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Ash for treatment, Re-processing of ash into clinker</t>
+          <t>Water Consumption Blue - Manufacturing - Secondary other non-ferrous metals for treatment, Re-processing of secondary other non-ferrous metals into new other non-ferrous metals</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Other non-metallic mineral products</t>
+          <t>Water Consumption Blue - Manufacturing - Fabricated metal products, except machinery and equipment (28)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Basic iron and steel and of ferro-alloys and first products thereof</t>
+          <t>Water Consumption Blue - Manufacturing - Machinery and equipment n.e.c. (29)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Secondary steel for treatment, Re-processing of secondary steel into new steel</t>
+          <t>Water Consumption Blue - Manufacturing - Office machinery and computers (30)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Precious metals</t>
+          <t>Water Consumption Blue - Manufacturing - Electrical machinery and apparatus n.e.c. (31)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Secondary preciuos metals for treatment, Re-processing of secondary preciuos metals into new preciuos metals</t>
+          <t>Water Consumption Blue - Manufacturing - Radio, television and communication equipment and apparatus (32)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Aluminium and aluminium products</t>
+          <t>Water Consumption Blue - Manufacturing - Medical, precision and optical instruments, watches and clocks (33)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Secondary aluminium for treatment, Re-processing of secondary aluminium into new aluminium</t>
+          <t>Water Consumption Blue - Manufacturing - Motor vehicles, trailers and semi-trailers (34)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Lead, zinc and tin and products thereof</t>
+          <t>Water Consumption Blue - Manufacturing - Other transport equipment (35)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Secondary lead for treatment, Re-processing of secondary lead into new lead</t>
+          <t>Water Consumption Blue - Manufacturing - Furniture; other manufactured goods n.e.c. (36)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Copper products</t>
+          <t>Water Consumption Blue - Electricity - tower - Electricity by coal</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Secondary copper for treatment, Re-processing of secondary copper into new copper</t>
+          <t>Water Consumption Blue - Electricity - tower - Electricity by gas</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Other non-ferrous metal products</t>
+          <t>Water Consumption Blue - Electricity - tower - Electricity by nuclear</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Secondary other non-ferrous metals for treatment, Re-processing of secondary other non-ferrous metals into new other non-ferrous metals</t>
+          <t>Water Consumption Blue - Electricity - tower - Electricity by hydro</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Fabricated metal products, except machinery and equipment (28)</t>
+          <t>Water Consumption Blue - Electricity - tower - Electricity by wind</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Machinery and equipment n.e.c. (29)</t>
+          <t>Water Consumption Blue - Electricity - tower - Electricity by petroleum and other oil derivatives</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Office machinery and computers (30)</t>
+          <t>Water Consumption Blue - Electricity - tower - Electricity by biomass and waste</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Electrical machinery and apparatus n.e.c. (31)</t>
+          <t>Water Consumption Blue - Electricity - tower - Electricity by solar photovoltaic</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Radio, television and communication equipment and apparatus (32)</t>
+          <t>Water Consumption Blue - Electricity - tower - Electricity by solar thermal</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Medical, precision and optical instruments, watches and clocks (33)</t>
+          <t>Water Consumption Blue - Electricity - tower - Electricity by tide, wave, ocean</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Motor vehicles, trailers and semi-trailers (34)</t>
+          <t>Water Consumption Blue - Electricity - tower - Electricity by Geothermal</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Other transport equipment (35)</t>
+          <t>Water Consumption Blue - Electricity - tower - Electricity nec</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Manufacturing - Furniture; other manufactured goods n.e.c. (36)</t>
+          <t>Water Consumption Blue - Electricity - once-through - Electricity by coal</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Electricity - tower - Electricity by coal</t>
+          <t>Water Consumption Blue - Electricity - once-through - Electricity by gas</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Electricity - tower - Electricity by gas</t>
+          <t>Water Consumption Blue - Electricity - once-through - Electricity by nuclear</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Electricity - tower - Electricity by nuclear</t>
+          <t>Water Consumption Blue - Electricity - once-through - Electricity by hydro</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Electricity - tower - Electricity by hydro</t>
+          <t>Water Consumption Blue - Electricity - once-through - Electricity by wind</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Electricity - tower - Electricity by wind</t>
+          <t>Water Consumption Blue - Electricity - once-through - Electricity by petroleum and other oil derivatives</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Electricity - tower - Electricity by petroleum and other oil derivatives</t>
+          <t>Water Consumption Blue - Electricity - once-through - Electricity by biomass and waste</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Electricity - tower - Electricity by biomass and waste</t>
+          <t>Water Consumption Blue - Electricity - once-through - Electricity by solar photovoltaic</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Electricity - tower - Electricity by solar photovoltaic</t>
+          <t>Water Consumption Blue - Electricity - once-through - Electricity by solar thermal</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Electricity - tower - Electricity by solar thermal</t>
+          <t>Water Consumption Blue - Electricity - once-through - Electricity by tide, wave, ocean</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Electricity - tower - Electricity by tide, wave, ocean</t>
+          <t>Water Consumption Blue - Electricity - once-through - Electricity by Geothermal</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Electricity - tower - Electricity by Geothermal</t>
+          <t>Water Consumption Blue - Electricity - once-through - Electricity nec</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Water Consumption Blue - Electricity - tower - Electricity nec</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Water Consumption Blue - Electricity - once-through - Electricity by coal</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Water Consumption Blue - Electricity - once-through - Electricity by gas</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Water Consumption Blue - Electricity - once-through - Electricity by nuclear</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Water Consumption Blue - Electricity - once-through - Electricity by hydro</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Water Consumption Blue - Electricity - once-through - Electricity by wind</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Water Consumption Blue - Electricity - once-through - Electricity by petroleum and other oil derivatives</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Water Consumption Blue - Electricity - once-through - Electricity by biomass and waste</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Water Consumption Blue - Electricity - once-through - Electricity by solar photovoltaic</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Water Consumption Blue - Electricity - once-through - Electricity by solar thermal</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Water Consumption Blue - Electricity - once-through - Electricity by tide, wave, ocean</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Water Consumption Blue - Electricity - once-through - Electricity by Geothermal</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Water Consumption Blue - Electricity - once-through - Electricity nec</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
           <t>Water Consumption Blue - Domestic - domestic Water Consumption Blue</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Products of meat cattle</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Products of meat pigs</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Products of meat poultry</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Meat products nec</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - products of Vegetable oils and fats</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Dairy products</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Processed rice</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Sugar</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Food products nec</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Beverages</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Fish products</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Tobacco products (16)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Textiles (17)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Wearing apparel; furs (18)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Leather and leather products (19)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Pulp</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Secondary paper for treatment, Re-processing of secondary paper into new pulp</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Paper and paper products</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Printed matter and recorded media (22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Plastics, basic</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Secondary plastic for treatment, Re-processing of secondary plastic into new plastic</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - N-fertiliser</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - P- and other fertiliser</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Chemicals nec</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Rubber and plastic products (25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Glass and glass products</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Secondary glass for treatment, Re-processing of secondary glass into new glass</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Ceramic goods</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Bricks, tiles and construction products, in baked clay</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Cement, lime and plaster</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Ash for treatment, Re-processing of ash into clinker</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Other non-metallic mineral products</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Basic iron and steel and of ferro-alloys and first products thereof</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Secondary steel for treatment, Re-processing of secondary steel into new steel</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Precious metals</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Secondary preciuos metals for treatment, Re-processing of secondary preciuos metals into new preciuos metals</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Aluminium and aluminium products</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Secondary aluminium for treatment, Re-processing of secondary aluminium into new aluminium</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Lead, zinc and tin and products thereof</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Secondary lead for treatment, Re-processing of secondary lead into new lead</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Copper products</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Secondary copper for treatment, Re-processing of secondary copper into new copper</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Other non-ferrous metal products</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Secondary other non-ferrous metals for treatment, Re-processing of secondary other non-ferrous metals into new other non-ferrous metals</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Fabricated metal products, except machinery and equipment (28)</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Machinery and equipment n.e.c. (29)</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Office machinery and computers (30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Electrical machinery and apparatus n.e.c. (31)</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Radio, television and communication equipment and apparatus (32)</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Medical, precision and optical instruments, watches and clocks (33)</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Motor vehicles, trailers and semi-trailers (34)</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Other transport equipment (35)</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Manufacturing - Furniture; other manufactured goods n.e.c. (36)</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - tower - Electricity by coal</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - tower - Electricity by gas</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - tower - Electricity by nuclear</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - tower - Electricity by hydro</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - tower - Electricity by wind</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - tower - Electricity by petroleum and other oil derivatives</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - tower - Electricity by biomass and waste</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - tower - Electricity by solar photovoltaic</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - tower - Electricity by solar thermal</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - tower - Electricity by tide, wave, ocean</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - tower - Electricity by Geothermal</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - tower - Electricity nec</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - once-through - Electricity by coal</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - once-through - Electricity by gas</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - once-through - Electricity by nuclear</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - once-through - Electricity by hydro</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - once-through - Electricity by wind</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - once-through - Electricity by petroleum and other oil derivatives</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - once-through - Electricity by biomass and waste</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - once-through - Electricity by solar photovoltaic</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - once-through - Electricity by solar thermal</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - once-through - Electricity by tide, wave, ocean</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - once-through - Electricity by Geothermal</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Electricity - once-through - Electricity nec</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Water Withdrawal Blue - Domestic - domestic Water Withdrawal Blue</t>
         </is>
       </c>
     </row>
